--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/tarapaca.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2508.26</v>
+        <v>2487.02</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>812.23</v>
+        <v>805.35</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4274.89</v>
+        <v>4232.22</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5343.61</v>
+        <v>5290.28</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>19168.59</v>
+        <v>18967.85</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>10687.22</v>
+        <v>10668.26</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>9084.129999999999</v>
+        <v>9148.24</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1588.85</v>
+        <v>1600.06</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>829.55</v>
+        <v>819.01</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>18610.88</v>
+        <v>18532.86</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>18610.88</v>
+        <v>18453.23</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>61634.23</v>
+        <v>61971.29</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>12443.92</v>
+        <v>12461.2</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>176.79</v>
+        <v>176.18</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>4745.33</v>
+        <v>4715.59</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>859.76</v>
+        <v>865.4</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>23082.7</v>
+        <v>23201.94</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>19800.95</v>
+        <v>19849.67</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4052.07</v>
+        <v>3999.9</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>339.85</v>
+        <v>337.45</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1556.74</v>
+        <v>1538.77</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2198.06</v>
+        <v>2166.26</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>25652.19</v>
+        <v>24965.32</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>846.4299999999999</v>
+        <v>857.48</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>556.86</v>
+        <v>570.5700000000001</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1670.59</v>
+        <v>1711.7</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>16705.9</v>
+        <v>17021.86</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>219.54</v>
+        <v>223.7</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>846.67</v>
+        <v>841.59</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>11855.45</v>
+        <v>11784.4</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>15367</v>
+        <v>15235.93</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>6426.2</v>
+        <v>6371.39</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3920.07</v>
+        <v>3886.63</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1114.03</v>
+        <v>1111.22</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>209.55</v>
+        <v>209.02</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3926.68</v>
+        <v>3972.74</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>15272.4</v>
+        <v>15156.54</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5508.29</v>
+        <v>5466.5</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>4109.66</v>
+        <v>4078.48</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>841.28</v>
+        <v>829.34</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>241.93</v>
+        <v>247.38</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>14221.85</v>
+        <v>14320.04</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1480.41</v>
+        <v>1484.99</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>395.29</v>
+        <v>399.04</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>592.9299999999999</v>
+        <v>598.5599999999999</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>3109.66</v>
+        <v>3139.2</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>107.41</v>
+        <v>108.5</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>982.09</v>
+        <v>991.9299999999999</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>7489.71</v>
+        <v>7527.88</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>14732.05</v>
+        <v>14763.45</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>3951.71</v>
+        <v>3960.13</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>5933.87</v>
+        <v>5946.52</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,68 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>273.08</v>
+        <v>272.49</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1079967-454-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>54.68</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/tarapaca.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2013-1843-CM25</t>
+          <t>1407-15118-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2487.02</v>
+        <v>13700.51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2013-1928-CM25</t>
+          <t>1079967-339-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>805.35</v>
+        <v>18450.48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3349-351-CM25</t>
+          <t>1079967-413-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4232.22</v>
+        <v>2055.83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3413-87-CM25</t>
+          <t>1079967-412-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.971.700-7</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5290.28</v>
+        <v>17063.46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1079967-632-CM25</t>
+          <t>1079967-488-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>18967.85</v>
+        <v>18223.81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1407-15784-CM25</t>
+          <t>3349-336-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>10668.26</v>
+        <v>4190.64</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1407-15835-CM25</t>
+          <t>2013-1843-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,22 +895,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>9148.24</v>
+        <v>2487.02</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2948-350-CM25</t>
+          <t>2013-1928-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.102.051-1</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Comandancia en Jefe de la IV Zona Naval</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1600.06</v>
+        <v>805.35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2013-2005-CM25</t>
+          <t>3349-351-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>819.01</v>
+        <v>4232.22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1079967-711-CM25</t>
+          <t>3413-87-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.971.700-7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>18532.86</v>
+        <v>5290.28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1079967-718-CM25</t>
+          <t>1079967-632-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>18453.23</v>
+        <v>18967.85</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>707412-143-CM25</t>
+          <t>1407-15784-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>61971.29</v>
+        <v>10668.26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1407-13-CM26</t>
+          <t>2948-350-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.102.051-1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>Comandancia en Jefe de la IV Zona Naval</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>12461.2</v>
+        <v>1600.06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2013-25-CM26</t>
+          <t>1407-15835-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,27 +1317,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>176.18</v>
+        <v>9148.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>707412-5-CM26</t>
+          <t>2013-2005-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,27 +1378,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>4715.59</v>
+        <v>819.01</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2013-40-CM26</t>
+          <t>1079967-711-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>865.4</v>
+        <v>18532.86</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1079967-35-CM26</t>
+          <t>1079967-718-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>23201.94</v>
+        <v>18453.23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1079967-77-CM26</t>
+          <t>707412-143-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>19849.67</v>
+        <v>61971.29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1079967-80-CM26</t>
+          <t>1407-13-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3999.9</v>
+        <v>12461.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2013-263-CM26</t>
+          <t>2013-25-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>337.45</v>
+        <v>176.18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1288512-14-CM26</t>
+          <t>707412-5-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE TARAPACÁ</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1538.77</v>
+        <v>4715.59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3413-12-CM26</t>
+          <t>2013-40-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.971.700-7</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2166.26</v>
+        <v>865.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1079967-167-CM26</t>
+          <t>1079967-35-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>24965.32</v>
+        <v>23201.94</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2013-287-CM26</t>
+          <t>1079967-77-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>857.48</v>
+        <v>19849.67</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1079967-184-CM26</t>
+          <t>1079967-80-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>570.5700000000001</v>
+        <v>3999.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1079967-185-CM26</t>
+          <t>2013-263-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1711.7</v>
+        <v>337.45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3349-118-CM26</t>
+          <t>1288512-14-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCIÓN REGIONAL DE TARAPACÁ</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>17021.86</v>
+        <v>1538.77</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2013-623-CM26</t>
+          <t>3413-12-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,27 +2171,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.971.700-7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>223.7</v>
+        <v>2166.26</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2013-646-CM26</t>
+          <t>1079967-167-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,27 +2232,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>841.59</v>
+        <v>24965.32</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2013-684-CM26</t>
+          <t>2013-287-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>11784.4</v>
+        <v>857.48</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1079967-222-CM26</t>
+          <t>1079967-184-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>15235.93</v>
+        <v>570.5700000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1079967-223-CM26</t>
+          <t>1079967-185-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>6371.39</v>
+        <v>1711.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1079967-224-CM26</t>
+          <t>2013-623-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,27 +2476,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3886.63</v>
+        <v>223.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3349-129-CM26</t>
+          <t>3349-118-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1111.22</v>
+        <v>17021.86</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2013-775-CM26</t>
+          <t>2013-646-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>209.02</v>
+        <v>841.59</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2013-845-CM26</t>
+          <t>2013-684-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3972.74</v>
+        <v>11784.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1079967-294-CM26</t>
+          <t>1079967-222-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>15156.54</v>
+        <v>15235.93</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1079967-295-CM26</t>
+          <t>1079967-223-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5466.5</v>
+        <v>6371.39</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1079967-296-CM26</t>
+          <t>1079967-224-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>4078.48</v>
+        <v>3886.63</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2013-936-CM26</t>
+          <t>3349-129-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,27 +2903,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>829.34</v>
+        <v>1111.22</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2013-1017-CM26</t>
+          <t>2013-775-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>247.38</v>
+        <v>209.02</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2013-1021-CM26</t>
+          <t>2013-845-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3070,18 +3070,18 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>14320.04</v>
+        <v>3972.74</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3413-53-CM26</t>
+          <t>1079967-295-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.971.700-7</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3131,28 +3131,28 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1484.99</v>
+        <v>5466.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1079967-343-CM26</t>
+          <t>1079967-296-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3192,28 +3192,28 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>399.04</v>
+        <v>4078.48</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1079967-344-CM26</t>
+          <t>1079967-294-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3253,43 +3253,43 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>598.5599999999999</v>
+        <v>15156.54</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1079967-345-CM26</t>
+          <t>2013-936-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3314,43 +3314,43 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>3139.2</v>
+        <v>829.34</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1079967-370-CM26</t>
+          <t>2013-1017-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3375,28 +3375,28 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>108.5</v>
+        <v>247.38</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2013-1148-CM26</t>
+          <t>2013-1021-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>991.9299999999999</v>
+        <v>14320.04</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2013-1066-CM26</t>
+          <t>3413-53-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,27 +3452,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.971.700-7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>7527.88</v>
+        <v>1484.99</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1079967-401-CM26</t>
+          <t>1079967-343-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>14763.45</v>
+        <v>399.04</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1079967-403-CM26</t>
+          <t>1079967-344-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>3960.13</v>
+        <v>598.5599999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1079967-404-CM26</t>
+          <t>1079967-345-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>5946.52</v>
+        <v>3139.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2013-1214-CM26</t>
+          <t>1079967-370-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,22 +3701,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>272.49</v>
+        <v>108.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1079967-454-CM26</t>
+          <t>2013-1148-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,6 +3802,372 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
+        <v>991.9299999999999</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2013-1066-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>7527.88</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1079967-401-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>14763.45</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1079967-403-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>3960.13</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1079967-404-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>5946.52</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2013-1214-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>272.49</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1079967-454-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
         <v>54.68</v>
       </c>
     </row>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/tarapaca.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/tarapaca.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarapacá" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tarapacá" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1407-15118-CM25</t>
+          <t>3349-3-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>13700.51</v>
+        <v>1128.32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1079967-339-CM25</t>
+          <t>3349-15-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>18450.48</v>
+        <v>1996.15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1079967-413-CM25</t>
+          <t>2013-37-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2055.83</v>
+        <v>274.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1079967-412-CM25</t>
+          <t>1407-15059-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>17063.46</v>
+        <v>15119.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1079967-488-CM25</t>
+          <t>707412-2-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>18223.81</v>
+        <v>40365.71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3349-336-CM25</t>
+          <t>3349-26-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>4190.64</v>
+        <v>1524.03</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2013-1843-CM25</t>
+          <t>3349-28-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2487.02</v>
+        <v>8267.959999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2013-1928-CM25</t>
+          <t>3349-30-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>805.35</v>
+        <v>2082.03</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3349-351-CM25</t>
+          <t>1079967-27-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>4232.22</v>
+        <v>13270.92</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3413-87-CM25</t>
+          <t>1079967-34-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.971.700-7</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5290.28</v>
+        <v>3739.39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1079967-632-CM25</t>
+          <t>1288512-8-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>18967.85</v>
+        <v>1822.85</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1407-15784-CM25</t>
+          <t>1407-15118-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>10668.26</v>
+        <v>13700.51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2948-350-CM25</t>
+          <t>3349-53-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.102.051-1</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Comandancia en Jefe de la IV Zona Naval</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1600.06</v>
+        <v>3202.73</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1407-15835-CM25</t>
+          <t>1079967-60-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>9148.24</v>
+        <v>15900.54</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2013-2005-CM25</t>
+          <t>2013-186-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>819.01</v>
+        <v>193.61</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1079967-711-CM25</t>
+          <t>2013-245-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>18532.86</v>
+        <v>1437.02</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1079967-718-CM25</t>
+          <t>1407-15168-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>18453.23</v>
+        <v>16287</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>707412-143-CM25</t>
+          <t>1079967-117-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>61971.29</v>
+        <v>2084.37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1407-13-CM26</t>
+          <t>1079967-147-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>12461.2</v>
+        <v>18054.57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2013-25-CM26</t>
+          <t>2013-365-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>176.18</v>
+        <v>198.36</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>707412-5-CM26</t>
+          <t>3349-107-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>4715.59</v>
+        <v>5112</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2013-40-CM26</t>
+          <t>1407-15227-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>865.4</v>
+        <v>6018.71</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1079967-35-CM26</t>
+          <t>3349-106-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>23201.94</v>
+        <v>2132.15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1079967-77-CM26</t>
+          <t>707412-29-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>19849.67</v>
+        <v>3448.72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1079967-80-CM26</t>
+          <t>1079967-193-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3999.9</v>
+        <v>18921.32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2013-263-CM26</t>
+          <t>1407-15283-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>337.45</v>
+        <v>8485.17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1288512-14-CM26</t>
+          <t>3413-22-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.971.700-7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE TARAPACÁ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1538.77</v>
+        <v>6374.84</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3413-12-CM26</t>
+          <t>2013-542-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,27 +2171,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.971.700-7</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2166.26</v>
+        <v>808.36</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1079967-167-CM26</t>
+          <t>3349-136-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>24965.32</v>
+        <v>3249.15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2013-287-CM26</t>
+          <t>2013-517-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>857.48</v>
+        <v>209.83</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1079967-184-CM26</t>
+          <t>3349-144-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>570.5700000000001</v>
+        <v>2085.74</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1079967-185-CM26</t>
+          <t>1407-15316-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1711.7</v>
+        <v>27737.18</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2013-623-CM26</t>
+          <t>2013-592-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>223.7</v>
+        <v>806.8200000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3349-118-CM26</t>
+          <t>2013-672-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,27 +2537,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>17021.86</v>
+        <v>711.01</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2013-646-CM26</t>
+          <t>3349-198-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,27 +2598,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>841.59</v>
+        <v>2655.24</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2013-684-CM26</t>
+          <t>3349-196-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,27 +2659,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>11784.4</v>
+        <v>2656.53</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1079967-222-CM26</t>
+          <t>2013-737-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,27 +2720,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>15235.93</v>
+        <v>3261.96</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1079967-223-CM26</t>
+          <t>1079967-266-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>6371.39</v>
+        <v>18811.39</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1079967-224-CM26</t>
+          <t>3413-35-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.971.700-7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>3886.63</v>
+        <v>2293.36</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3349-129-CM26</t>
+          <t>1196-129-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1111.22</v>
+        <v>752.77</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2013-775-CM26</t>
+          <t>2013-835-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>209.02</v>
+        <v>205.44</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2013-845-CM26</t>
+          <t>6-137-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,27 +3025,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.838.000-9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION I REGION</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3972.74</v>
+        <v>1667.09</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1079967-295-CM26</t>
+          <t>2948-203-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.102.051-1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>5466.5</v>
+        <v>1025.12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1079967-296-CM26</t>
+          <t>2013-853-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,27 +3147,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>4078.48</v>
+        <v>814.21</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1079967-294-CM26</t>
+          <t>2013-882-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>15156.54</v>
+        <v>1493.94</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2013-936-CM26</t>
+          <t>1079967-339-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,27 +3269,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>829.34</v>
+        <v>18450.48</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2013-1017-CM26</t>
+          <t>1407-15429-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,27 +3330,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>247.38</v>
+        <v>10808.36</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2013-1021-CM26</t>
+          <t>2013-1003-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3436,28 +3436,28 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>14320.04</v>
+        <v>191.41</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3413-53-CM26</t>
+          <t>3349-237-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.971.700-7</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3497,28 +3497,28 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1484.99</v>
+        <v>2621.59</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1079967-343-CM26</t>
+          <t>3349-241-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3558,43 +3558,43 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>399.04</v>
+        <v>2634.55</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1079967-344-CM26</t>
+          <t>2013-1094-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3619,43 +3619,43 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>598.5599999999999</v>
+        <v>1493.86</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1079967-345-CM26</t>
+          <t>2013-1150-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3680,28 +3680,28 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3139.2</v>
+        <v>785.55</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1079967-370-CM26</t>
+          <t>3349-268-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3741,43 +3741,43 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>108.5</v>
+        <v>1552.76</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2013-1148-CM26</t>
+          <t>3349-274-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3802,43 +3802,43 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>991.9299999999999</v>
+        <v>1265.32</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2013-1066-CM26</t>
+          <t>1079967-412-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3863,28 +3863,28 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>7527.88</v>
+        <v>17063.46</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1079967-401-CM26</t>
+          <t>1079967-413-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3924,28 +3924,28 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>14763.45</v>
+        <v>2055.83</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1079967-403-CM26</t>
+          <t>3349-285-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3985,43 +3985,43 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3960.13</v>
+        <v>3119.02</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1079967-404-CM26</t>
+          <t>2013-1225-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4046,43 +4046,43 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5946.52</v>
+        <v>204.95</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2013-1214-CM26</t>
+          <t>1407-15571-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4107,28 +4107,28 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>272.49</v>
+        <v>14503.56</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1079967-454-CM26</t>
+          <t>2013-1333-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,6 +4168,4520 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
+        <v>1029.84</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2013-1388-CM25</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>783.9400000000001</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>802-58-CM25</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>72.396.000-2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>257.41</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1079967-488-CM25</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>18223.81</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>3349-294-CM25</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>65.283.230-K</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>2288.03</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2013-1552-CM25</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>656.22</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2013-1478-CM25</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>104.89</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2013-1611-CM25</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>789.7</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1079967-555-CM25</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>17732.67</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>3349-336-CM25</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>65.283.230-K</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>4190.64</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>3349-338-CM25</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>65.283.230-K</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>3634.14</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2013-1755-CM25</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>1043.25</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1407-15666-CM25</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>61.004.002-0</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>10399.23</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>707412-91-CM25</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>8000.89</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3349-331-CM25</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>65.283.230-K</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>2521.59</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2948-294-CM25</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>61.102.051-1</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>1626.87</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1407-15729-CM25</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>61.004.002-0</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>10631.85</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2013-1928-CM25</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>805.35</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2013-1843-CM25</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>2487.02</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>3349-351-CM25</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>65.283.230-K</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>4232.22</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>3413-87-CM25</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>61.971.700-7</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>5290.28</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1079967-632-CM25</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>18967.85</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1407-15784-CM25</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>61.004.002-0</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>10668.26</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1407-15835-CM25</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>61.004.002-0</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>9148.24</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2948-350-CM25</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>61.102.051-1</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Comandancia en Jefe de la IV Zona Naval</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>1600.06</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2013-2005-CM25</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>819.01</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1079967-711-CM25</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>18532.86</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1079967-718-CM25</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>18453.23</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>707412-143-CM25</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>61971.29</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1407-13-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>61.004.002-0</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>12461.2</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2013-25-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>176.18</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>707412-5-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>4715.59</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2013-40-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>865.4</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1079967-35-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>23201.94</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1079967-77-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>19849.67</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1079967-80-CM26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>3999.9</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2013-263-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>337.45</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1288512-14-CM26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>60.905.000-4</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>DIRECCIÓN REGIONAL DE TARAPACÁ</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>1538.77</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>3413-12-CM26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>61.971.700-7</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>2166.26</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1079967-167-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>24965.32</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2013-287-CM26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>857.48</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1079967-185-CM26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>1711.7</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1079967-184-CM26</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>570.5700000000001</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2013-623-CM26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>223.7</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>3349-118-CM26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>65.283.230-K</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>17021.86</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2013-646-CM26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>841.59</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2013-684-CM26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>11784.4</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1079967-222-CM26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>15235.93</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1079967-223-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>6371.39</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1079967-224-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>3886.63</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>3349-129-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>65.283.230-K</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>1111.22</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2013-775-CM26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>209.02</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2013-845-CM26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>3972.74</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1079967-294-CM26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>15156.54</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1079967-295-CM26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>5466.5</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1079967-296-CM26</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>4078.48</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2013-936-CM26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>829.34</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2013-1017-CM26</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>247.38</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2013-1021-CM26</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>14320.04</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>3413-53-CM26</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>61.971.700-7</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>1484.99</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1079967-343-CM26</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>399.04</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1079967-344-CM26</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>598.5599999999999</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1079967-345-CM26</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>3139.2</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1079967-370-CM26</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>108.5</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2013-1148-CM26</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>991.9299999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2013-1066-CM26</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>7527.88</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1079967-401-CM26</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>14763.45</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1079967-403-CM26</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>3960.13</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>1079967-404-CM26</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS I ZONA</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>5946.52</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2013-1214-CM26</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>272.49</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2013-1290-CM26</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>988.55</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>1079967-442-CM26</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>15300.24</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>1079967-444-CM26</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>5749.28</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>1079967-445-CM26</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>3972.58</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>1079967-454-CM26</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="n">
         <v>54.68</v>
       </c>
     </row>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/tarapaca.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M135"/>
+  <dimension ref="A1:M141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2588,7 +2588,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3349-198-CM25</t>
+          <t>3349-196-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2655.24</v>
+        <v>2656.53</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3349-196-CM25</t>
+          <t>3349-198-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2656.53</v>
+        <v>2655.24</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2013-737-CM25</t>
+          <t>1079967-266-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2730,17 +2730,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3261.96</v>
+        <v>18811.39</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1079967-266-CM25</t>
+          <t>2013-737-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2791,17 +2791,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>18811.39</v>
+        <v>3261.96</v>
       </c>
     </row>
     <row r="40">
@@ -3259,7 +3259,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1079967-339-CM25</t>
+          <t>1407-15429-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>18450.48</v>
+        <v>10808.36</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1407-15429-CM25</t>
+          <t>1079967-339-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>10808.36</v>
+        <v>18450.48</v>
       </c>
     </row>
     <row r="49">
@@ -3686,7 +3686,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3349-268-CM25</t>
+          <t>3349-274-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1552.76</v>
+        <v>1265.32</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3349-274-CM25</t>
+          <t>3349-268-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1265.32</v>
+        <v>1552.76</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1079967-412-CM25</t>
+          <t>1079967-413-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>17063.46</v>
+        <v>2055.83</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1079967-413-CM25</t>
+          <t>1079967-412-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2055.83</v>
+        <v>17063.46</v>
       </c>
     </row>
     <row r="58">
@@ -4784,7 +4784,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2013-1755-CM25</t>
+          <t>1407-15666-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4804,17 +4804,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1043.25</v>
+        <v>10399.23</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1407-15666-CM25</t>
+          <t>2013-1755-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4865,17 +4865,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>10399.23</v>
+        <v>1043.25</v>
       </c>
     </row>
     <row r="74">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Comandancia en Jefe de la IV Zona Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE TARAPACÁ</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6614,7 +6614,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1079967-185-CM26</t>
+          <t>1079967-184-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1711.7</v>
+        <v>570.5700000000001</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1079967-184-CM26</t>
+          <t>1079967-185-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>570.5700000000001</v>
+        <v>1711.7</v>
       </c>
     </row>
     <row r="104">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6858,7 +6858,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2013-646-CM26</t>
+          <t>2013-684-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>841.59</v>
+        <v>11784.4</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2013-684-CM26</t>
+          <t>2013-646-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>11784.4</v>
+        <v>841.59</v>
       </c>
     </row>
     <row r="108">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8683,6 +8683,372 @@
       </c>
       <c r="M135" s="2" t="n">
         <v>54.68</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2013-1441-CM26</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>12810.22</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>1079967-510-CM26</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>15440.23</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>1079967-517-CM26</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>4115.72</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>1079967-518-CM26</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>5865.21</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2013-1453-CM26</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>845.79</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2013-1473-CM26</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/tarapaca.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/tarapaca.xlsx
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +8037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +9012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9207,11 @@
           <t>96.556.930-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/tarapaca.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M141"/>
+  <dimension ref="A1:M147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2334,7 +2334,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3349-136-CM25</t>
+          <t>2013-517-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2393,13 +2393,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3249.15</v>
+        <v>209.83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2013-517-CM25</t>
+          <t>3349-136-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2419,17 +2419,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>209.83</v>
+        <v>3249.15</v>
       </c>
     </row>
     <row r="32">
@@ -2594,7 +2594,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2013-592-CM25</t>
+          <t>2013-672-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>806.8200000000001</v>
+        <v>711.01</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2013-672-CM25</t>
+          <t>2013-592-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2718,7 +2718,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>711.01</v>
+        <v>806.8200000000001</v>
       </c>
     </row>
     <row r="36">
@@ -2854,7 +2854,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1079967-266-CM25</t>
+          <t>2013-737-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2874,17 +2874,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2913,13 +2913,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>18811.39</v>
+        <v>3261.96</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2013-737-CM25</t>
+          <t>1079967-266-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2939,17 +2939,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3261.96</v>
+        <v>18811.39</v>
       </c>
     </row>
     <row r="40">
@@ -5454,7 +5454,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2013-1928-CM25</t>
+          <t>2013-1843-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5513,13 +5513,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>805.35</v>
+        <v>2487.02</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2013-1843-CM25</t>
+          <t>2013-1928-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5578,13 +5578,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2487.02</v>
+        <v>805.35</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3349-351-CM25</t>
+          <t>3413-87-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.971.700-7</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5643,13 +5643,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>4232.22</v>
+        <v>5290.28</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3413-87-CM25</t>
+          <t>3349-351-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.971.700-7</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>5290.28</v>
+        <v>4232.22</v>
       </c>
     </row>
     <row r="82">
@@ -7014,7 +7014,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1079967-184-CM26</t>
+          <t>1079967-185-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7073,13 +7073,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>570.5700000000001</v>
+        <v>1711.7</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1079967-185-CM26</t>
+          <t>1079967-184-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7138,13 +7138,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1711.7</v>
+        <v>570.5700000000001</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2013-623-CM26</t>
+          <t>3349-118-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7164,17 +7164,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7203,13 +7203,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>223.7</v>
+        <v>17021.86</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3349-118-CM26</t>
+          <t>2013-623-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7229,17 +7229,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>17021.86</v>
+        <v>223.7</v>
       </c>
     </row>
     <row r="106">
@@ -7404,7 +7404,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1079967-222-CM26</t>
+          <t>1079967-223-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7463,13 +7463,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>15235.93</v>
+        <v>6371.39</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1079967-223-CM26</t>
+          <t>1079967-224-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7528,13 +7528,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>6371.39</v>
+        <v>3886.63</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1079967-224-CM26</t>
+          <t>1079967-222-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7593,13 +7593,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>3886.63</v>
+        <v>15235.93</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3349-129-CM26</t>
+          <t>2013-775-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7619,17 +7619,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7658,13 +7658,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1111.22</v>
+        <v>209.02</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2013-775-CM26</t>
+          <t>3349-129-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7684,17 +7684,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>209.02</v>
+        <v>1111.22</v>
       </c>
     </row>
     <row r="113">
@@ -7859,7 +7859,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1079967-295-CM26</t>
+          <t>1079967-296-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>5466.5</v>
+        <v>4078.48</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1079967-296-CM26</t>
+          <t>1079967-295-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>4078.48</v>
+        <v>5466.5</v>
       </c>
     </row>
     <row r="117">
@@ -8249,7 +8249,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1079967-343-CM26</t>
+          <t>1079967-344-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8308,13 +8308,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>399.04</v>
+        <v>598.5599999999999</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1079967-344-CM26</t>
+          <t>1079967-343-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8373,7 +8373,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>598.5599999999999</v>
+        <v>399.04</v>
       </c>
     </row>
     <row r="123">
@@ -8639,7 +8639,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1079967-401-CM26</t>
+          <t>1079967-404-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8698,7 +8698,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>14763.45</v>
+        <v>5946.52</v>
       </c>
     </row>
     <row r="128">
@@ -8769,7 +8769,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1079967-404-CM26</t>
+          <t>1079967-401-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>5946.52</v>
+        <v>14763.45</v>
       </c>
     </row>
     <row r="130">
@@ -9289,7 +9289,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1079967-510-CM26</t>
+          <t>1079967-518-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9348,7 +9348,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>15440.23</v>
+        <v>5865.21</v>
       </c>
     </row>
     <row r="138">
@@ -9419,7 +9419,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1079967-518-CM26</t>
+          <t>1079967-510-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>5865.21</v>
+        <v>15440.23</v>
       </c>
     </row>
     <row r="140">
@@ -9609,6 +9609,396 @@
       </c>
       <c r="M141" s="2" t="n">
         <v>214</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2013-1575-CM26</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>5270.08</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2013-1577-CM26</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>796.08</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2404-1330-CM26</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>69.010.300-1</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>3571.98</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>1079967-579-CM26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>13744.42</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>1079967-577-CM26</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>3620.05</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>1079967-576-CM26</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>5082.65</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/tarapaca.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/tarapaca.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
